--- a/grupos/3ARHV - Estadisticos 20231.xlsx
+++ b/grupos/3ARHV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="134">
   <si>
     <t>Materia</t>
   </si>
@@ -2936,13 +2936,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>39</v>
@@ -2951,22 +2951,25 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2980,48 +2983,57 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3035,43 +3047,52 @@
         <v>91.7</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
         <v>80</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
       <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
         <v>80.59999999999999</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>91.7</v>
       </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
       <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
         <v>80</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
-      <c r="M4">
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
         <v>80.59999999999999</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>91.7</v>
       </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -3085,43 +3106,52 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
         <v>85</v>
       </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
       <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
         <v>94.40000000000001</v>
       </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
         <v>85</v>
       </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
-      <c r="M5">
+      <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
         <v>94.40000000000001</v>
       </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
       <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3135,7 +3165,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -3153,7 +3183,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3170,8 +3200,17 @@
       <c r="P6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3185,7 +3224,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3203,7 +3242,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3220,8 +3259,17 @@
       <c r="P7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3235,7 +3283,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -3253,7 +3301,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3270,8 +3318,17 @@
       <c r="P8">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -3285,43 +3342,52 @@
         <v>91.7</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>90</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>75</v>
       </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
       <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
         <v>77.8</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>91.7</v>
       </c>
-      <c r="J9">
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>90</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>75</v>
       </c>
-      <c r="L9">
-        <v>100</v>
-      </c>
-      <c r="M9">
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
         <v>77.8</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>91.7</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
         <v>90</v>
       </c>
-      <c r="P9">
+      <c r="S9">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3335,14 +3401,14 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
         <v>95</v>
       </c>
-      <c r="G10">
-        <v>100</v>
-      </c>
       <c r="H10">
         <v>100</v>
       </c>
@@ -3353,14 +3419,14 @@
         <v>100</v>
       </c>
       <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10">
         <v>95</v>
       </c>
-      <c r="L10">
-        <v>100</v>
-      </c>
-      <c r="M10">
-        <v>100</v>
-      </c>
       <c r="N10">
         <v>100</v>
       </c>
@@ -3368,10 +3434,19 @@
         <v>100</v>
       </c>
       <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3385,7 +3460,7 @@
         <v>91.7</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -3397,13 +3472,13 @@
         <v>100</v>
       </c>
       <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
         <v>91.7</v>
       </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
       <c r="K11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3412,39 +3487,48 @@
         <v>100</v>
       </c>
       <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
         <v>91.7</v>
       </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C12">
         <v>63.9</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>80</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>63.9</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>80</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>63.9</v>
       </c>
-      <c r="O12">
+      <c r="R12">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3461,40 +3545,49 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>75</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>80</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>77.8</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>91.7</v>
       </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
       <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>75</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>80</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>77.8</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>91.7</v>
       </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -3508,43 +3601,52 @@
         <v>95.8</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>90</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>80</v>
       </c>
-      <c r="G14">
-        <v>100</v>
-      </c>
       <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
         <v>86.09999999999999</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>95.8</v>
       </c>
-      <c r="J14">
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>90</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>80</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>86.09999999999999</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>95.8</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
         <v>90</v>
       </c>
-      <c r="P14">
+      <c r="S14">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -3558,7 +3660,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -3576,7 +3678,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3593,8 +3695,17 @@
       <c r="P15">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -3608,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -3626,7 +3737,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3643,8 +3754,17 @@
       <c r="P16">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -3658,7 +3778,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -3676,7 +3796,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -3693,8 +3813,17 @@
       <c r="P17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -3708,9 +3837,9 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>100</v>
-      </c>
-      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>100</v>
       </c>
       <c r="H18">
@@ -3722,20 +3851,29 @@
       <c r="J18">
         <v>100</v>
       </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
       <c r="L18">
         <v>100</v>
       </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -3749,14 +3887,14 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19">
+        <v>100</v>
+      </c>
+      <c r="G19">
         <v>95</v>
       </c>
-      <c r="G19">
-        <v>100</v>
-      </c>
       <c r="H19">
         <v>100</v>
       </c>
@@ -3767,14 +3905,14 @@
         <v>100</v>
       </c>
       <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
+      <c r="M19">
         <v>95</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
       <c r="N19">
         <v>100</v>
       </c>
@@ -3782,10 +3920,19 @@
         <v>100</v>
       </c>
       <c r="P19">
+        <v>100</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -3799,7 +3946,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -3817,7 +3964,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -3834,8 +3981,17 @@
       <c r="P20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -3849,7 +4005,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -3867,7 +4023,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -3884,8 +4040,17 @@
       <c r="P21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -3899,7 +4064,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -3917,7 +4082,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -3934,8 +4099,17 @@
       <c r="P22">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -3949,14 +4123,14 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
         <v>90</v>
       </c>
-      <c r="G23">
-        <v>100</v>
-      </c>
       <c r="H23">
         <v>100</v>
       </c>
@@ -3967,14 +4141,14 @@
         <v>100</v>
       </c>
       <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>100</v>
+      </c>
+      <c r="M23">
         <v>90</v>
       </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
       <c r="N23">
         <v>100</v>
       </c>
@@ -3982,10 +4156,19 @@
         <v>100</v>
       </c>
       <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -3999,7 +4182,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -4017,7 +4200,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4034,8 +4217,17 @@
       <c r="P24">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -4049,7 +4241,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -4067,7 +4259,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -4084,8 +4276,17 @@
       <c r="P25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -4099,14 +4300,14 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
         <v>90</v>
       </c>
-      <c r="G26">
-        <v>100</v>
-      </c>
       <c r="H26">
         <v>100</v>
       </c>
@@ -4117,14 +4318,14 @@
         <v>100</v>
       </c>
       <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26">
         <v>90</v>
       </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
       <c r="N26">
         <v>100</v>
       </c>
@@ -4132,10 +4333,19 @@
         <v>100</v>
       </c>
       <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -4149,7 +4359,7 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -4167,7 +4377,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4184,8 +4394,17 @@
       <c r="P27">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -4199,7 +4418,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -4217,7 +4436,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -4234,8 +4453,17 @@
       <c r="P28">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -4249,7 +4477,7 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -4267,7 +4495,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -4284,8 +4512,17 @@
       <c r="P29">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -4299,7 +4536,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -4317,7 +4554,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -4332,14 +4569,23 @@
         <v>100</v>
       </c>
       <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3ARHV - Estadisticos 20231.xlsx
+++ b/grupos/3ARHV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -176,6 +176,9 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -185,9 +188,6 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -203,223 +203,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERIAÑEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
   </si>
   <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>MERLIN</t>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>SAIRA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>KARYME CONCEPCION</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>ROSARIO DE JESUS</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>ALAN SANTIAGO</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>DEMY</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>ARAWY</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>AMERICA</t>
-  </si>
-  <si>
-    <t>ANDREA JANETH</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
   </si>
 </sst>
 </file>
@@ -918,7 +744,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -927,22 +753,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -963,16 +789,16 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -995,7 +821,7 @@
         <v>7</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -1004,22 +830,22 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1043,16 +869,16 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
+        <v>8</v>
+      </c>
+      <c r="W5">
+        <v>5</v>
+      </c>
+      <c r="X5">
         <v>7</v>
-      </c>
-      <c r="W5">
-        <v>-1</v>
-      </c>
-      <c r="X5">
-        <v>6</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1072,7 +898,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -1081,22 +907,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1123,13 +949,13 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1149,7 +975,7 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -1158,22 +984,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1203,10 +1029,10 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1226,7 +1052,7 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <v>6</v>
@@ -1235,22 +1061,22 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1274,16 +1100,16 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1303,7 +1129,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1312,22 +1138,22 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1357,7 +1183,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1380,7 +1206,7 @@
         <v>7</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -1389,22 +1215,22 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1425,22 +1251,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1457,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>9</v>
@@ -1466,22 +1292,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1508,16 +1334,16 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1531,10 +1357,10 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1563,31 +1389,31 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1617,10 +1443,10 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1640,7 +1466,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -1649,22 +1475,22 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1685,22 +1511,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1717,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1726,22 +1552,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1768,10 +1594,10 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1794,7 +1620,7 @@
         <v>7</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>8</v>
@@ -1803,22 +1629,22 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1839,22 +1665,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1871,7 +1697,7 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -1880,22 +1706,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1916,19 +1742,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -1948,25 +1774,25 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F18">
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1990,13 +1816,13 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2013,7 +1839,7 @@
         <v>10</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F19">
         <v>7</v>
@@ -2022,22 +1848,22 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2067,13 +1893,13 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2090,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -2099,22 +1925,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2141,10 +1967,10 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2167,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>6</v>
@@ -2176,22 +2002,22 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2215,16 +2041,16 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2244,7 +2070,7 @@
         <v>8</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>8</v>
@@ -2253,22 +2079,22 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2298,13 +2124,13 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2321,7 +2147,7 @@
         <v>7</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>6</v>
@@ -2330,22 +2156,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2366,22 +2192,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2398,7 +2224,7 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>9</v>
@@ -2407,22 +2233,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2449,16 +2275,16 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2475,7 +2301,7 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2484,22 +2310,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2520,22 +2346,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2552,7 +2378,7 @@
         <v>7</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -2561,22 +2387,22 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2603,13 +2429,13 @@
         <v>9</v>
       </c>
       <c r="V26">
+        <v>8</v>
+      </c>
+      <c r="W26">
         <v>7</v>
       </c>
-      <c r="W26">
-        <v>-1</v>
-      </c>
       <c r="X26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2629,7 +2455,7 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F27">
         <v>10</v>
@@ -2638,22 +2464,22 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2680,16 +2506,16 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2706,7 +2532,7 @@
         <v>9</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>10</v>
@@ -2715,22 +2541,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2757,10 +2583,10 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2783,7 +2609,7 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>10</v>
@@ -2792,22 +2618,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2834,16 +2660,16 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2860,7 +2686,7 @@
         <v>8</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F30">
         <v>7</v>
@@ -2869,22 +2695,22 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2905,16 +2731,16 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>9</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3047,7 +2873,7 @@
         <v>91.7</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -3059,37 +2885,37 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>80.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J4">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>80.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="P4">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3106,7 +2932,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -3118,37 +2944,37 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>94.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>94.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3165,7 +2991,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -3183,7 +3009,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3201,7 +3027,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3224,7 +3050,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3242,7 +3068,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3260,7 +3086,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3283,7 +3109,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -3301,13 +3127,13 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -3319,13 +3145,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3342,7 +3168,7 @@
         <v>91.7</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>90</v>
@@ -3354,37 +3180,37 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>77.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="J9">
-        <v>91.7</v>
+        <v>60.9</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M9">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9">
-        <v>77.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="P9">
-        <v>91.7</v>
+        <v>60.9</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S9">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3401,7 +3227,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -3416,10 +3242,10 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3434,10 +3260,10 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3460,7 +3286,7 @@
         <v>91.7</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -3475,10 +3301,10 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3493,10 +3319,10 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3516,16 +3342,16 @@
         <v>80</v>
       </c>
       <c r="I12">
-        <v>63.9</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="L12">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O12">
-        <v>63.9</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="R12">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3542,49 +3368,49 @@
         <v>91.7</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G13">
         <v>75</v>
       </c>
       <c r="H13">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I13">
-        <v>77.8</v>
+        <v>83.3</v>
       </c>
       <c r="J13">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M13">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="N13">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O13">
-        <v>77.8</v>
+        <v>83.3</v>
       </c>
       <c r="P13">
-        <v>91.7</v>
+        <v>91.3</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S13">
-        <v>75</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3601,7 +3427,7 @@
         <v>95.8</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>90</v>
@@ -3613,37 +3439,37 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>86.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="J14">
-        <v>95.8</v>
+        <v>93.5</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>90</v>
       </c>
       <c r="M14">
-        <v>80</v>
+        <v>67.5</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>86.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="P14">
-        <v>95.8</v>
+        <v>93.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
         <v>90</v>
       </c>
       <c r="S14">
-        <v>80</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3660,7 +3486,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -3678,7 +3504,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3696,7 +3522,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3719,7 +3545,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -3737,7 +3563,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3755,7 +3581,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -3778,7 +3604,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -3796,7 +3622,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -3814,7 +3640,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -3837,7 +3663,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -3852,7 +3678,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -3867,7 +3693,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -3887,7 +3713,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -3905,13 +3731,13 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -3923,13 +3749,13 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3946,7 +3772,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -3964,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -3982,7 +3808,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4005,7 +3831,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4023,13 +3849,13 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -4041,13 +3867,13 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4064,7 +3890,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -4082,13 +3908,13 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -4100,13 +3926,13 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4123,7 +3949,7 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -4138,16 +3964,16 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4156,16 +3982,16 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4182,7 +4008,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -4200,7 +4026,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4218,7 +4044,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4241,7 +4067,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -4259,13 +4085,13 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -4277,13 +4103,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4300,7 +4126,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -4318,13 +4144,13 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -4336,13 +4162,13 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4359,7 +4185,7 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -4377,7 +4203,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4395,7 +4221,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -4418,7 +4244,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -4436,13 +4262,13 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4454,13 +4280,13 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
         <v>100</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4477,7 +4303,7 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -4495,7 +4321,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -4513,7 +4339,7 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -4536,7 +4362,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -4554,7 +4380,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -4572,7 +4398,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -4644,48 +4470,51 @@
         <v>26</v>
       </c>
       <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>23.1</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>26</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
       </c>
       <c r="C3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>84.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="G3" s="2">
-        <v>15.4</v>
+        <v>16</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4696,39 +4525,39 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>85.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -4737,19 +4566,19 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>88.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="G5" s="2">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4760,28 +4589,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>8</v>
+        <v>11.1</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4829,7 +4658,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4856,546 +4685,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920392</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920205</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920207</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920393</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920210</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920394</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920211</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920213</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920213</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920374</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920214</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920215</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20322051180081</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920216</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920217</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>121</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920219</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920220</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920221</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920222</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>125</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920223</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920421</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920224</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920225</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920226</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920228</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" t="s">
-        <v>131</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920229</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5403,7 +4692,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5435,22 +4724,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920002</v>
+        <v>22330051920394</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5458,45 +4747,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920002</v>
+        <v>22330051920394</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920211</v>
+        <v>20330051920126</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5504,45 +4793,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920211</v>
+        <v>20330051920126</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920126</v>
+        <v>22330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5550,22 +4839,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920126</v>
+        <v>22330051920222</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5573,531 +4862,48 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920374</v>
+        <v>21330051920002</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920374</v>
+        <v>22330051920205</v>
       </c>
       <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" t="s">
-        <v>94</v>
-      </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G9">
         <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920392</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920205</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920207</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920393</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920394</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920214</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920215</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20322051180081</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920216</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920217</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920219</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920220</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920221</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920222</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920223</v>
-      </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920421</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920224</v>
-      </c>
-      <c r="B26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920225</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920226</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
-        <v>130</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920228</v>
-      </c>
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" t="s">
-        <v>131</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920229</v>
-      </c>
-      <c r="B30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" t="s">
-        <v>132</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>51</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3ARHV - Estadisticos 20231.xlsx
+++ b/grupos/3ARHV - Estadisticos 20231.xlsx
@@ -2461,7 +2461,7 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>10</v>
@@ -2515,7 +2515,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">

--- a/grupos/3ARHV - Estadisticos 20231.xlsx
+++ b/grupos/3ARHV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -173,24 +173,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -203,49 +203,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
   </si>
   <si>
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
   </si>
   <si>
     <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
   </si>
 </sst>
 </file>
@@ -771,31 +753,31 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -804,7 +786,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -848,22 +830,22 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -872,10 +854,10 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -925,22 +907,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -949,7 +931,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1002,22 +984,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1079,34 +1061,34 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1156,22 +1138,22 @@
         <v>3</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1233,22 +1215,22 @@
         <v>3</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1260,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1310,22 +1292,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1337,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1363,16 +1345,16 @@
         <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1416,28 +1398,28 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1446,7 +1428,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1493,22 +1475,22 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1517,16 +1499,16 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1570,22 +1552,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1594,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1647,28 +1629,28 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1680,7 +1662,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1724,40 +1706,40 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>8</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1795,19 +1777,19 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1819,7 +1801,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -1866,22 +1848,22 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -1899,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1943,22 +1925,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -1967,13 +1949,13 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2020,22 +2002,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2044,16 +2026,16 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2097,22 +2079,22 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2174,22 +2156,22 @@
         <v>3</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2198,16 +2180,16 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2251,22 +2233,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2328,31 +2310,31 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2361,7 +2343,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2405,28 +2387,28 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2438,7 +2420,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2482,22 +2464,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2509,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2559,22 +2541,22 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2636,22 +2618,22 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2713,22 +2695,22 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2740,10 +2722,10 @@
         <v>9</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2903,13 +2885,13 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>81.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="P4">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -2962,19 +2944,19 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>90.3</v>
+        <v>93.8</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3027,7 +3009,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3086,7 +3068,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3139,7 +3121,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="P8">
         <v>100</v>
@@ -3151,7 +3133,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3198,19 +3180,19 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>80.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="P9">
-        <v>60.9</v>
+        <v>42.4</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="R9">
-        <v>85</v>
+        <v>53.1</v>
       </c>
       <c r="S9">
-        <v>60</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3257,19 +3239,19 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P10">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R10">
         <v>100</v>
       </c>
       <c r="S10">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3319,10 +3301,10 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3348,10 +3330,10 @@
         <v>90</v>
       </c>
       <c r="O12">
-        <v>73.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="R12">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3395,22 +3377,22 @@
         <v>77.5</v>
       </c>
       <c r="N13">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O13">
-        <v>83.3</v>
+        <v>84.8</v>
       </c>
       <c r="P13">
-        <v>91.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S13">
-        <v>77.5</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3457,19 +3439,19 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>84.7</v>
+        <v>89.3</v>
       </c>
       <c r="P14">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="S14">
-        <v>67.5</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3516,13 +3498,13 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3581,7 +3563,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -3634,19 +3616,19 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3755,7 +3737,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3808,13 +3790,13 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R20">
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3861,19 +3843,19 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3926,13 +3908,13 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R22">
         <v>100</v>
       </c>
       <c r="S22">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3982,16 +3964,16 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4044,13 +4026,13 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4109,7 +4091,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4162,13 +4144,13 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>95</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4215,19 +4197,19 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P27">
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4280,13 +4262,13 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R28">
         <v>100</v>
       </c>
       <c r="S28">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4339,7 +4321,7 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -4398,7 +4380,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -4461,28 +4443,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>76.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="G2" s="2">
-        <v>23.1</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4493,28 +4475,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>84</v>
+        <v>88.5</v>
       </c>
       <c r="G3" s="2">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4525,7 +4507,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
@@ -4534,19 +4516,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>84.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G4" s="2">
-        <v>15.4</v>
+        <v>7.7</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4557,28 +4539,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>85.2</v>
+        <v>96.2</v>
       </c>
       <c r="G5" s="2">
-        <v>14.8</v>
+        <v>3.8</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4598,19 +4580,19 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>88.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="G6" s="2">
-        <v>11.1</v>
+        <v>3.7</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4621,28 +4603,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
       </c>
       <c r="C7">
+        <v>27</v>
+      </c>
+      <c r="D7">
         <v>26</v>
       </c>
-      <c r="D7">
-        <v>24</v>
-      </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>92.3</v>
+        <v>96.3</v>
       </c>
       <c r="G7" s="2">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4692,7 +4674,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4724,19 +4706,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920394</v>
+        <v>21330051920002</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>51</v>
@@ -4747,22 +4729,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920394</v>
+        <v>22330051920374</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4770,139 +4752,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920126</v>
+        <v>22330051920222</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920126</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920222</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920222</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920002</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920205</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20231.xlsx
+++ b/grupos/3ARHV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -203,6 +203,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
@@ -212,6 +215,9 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>ROCHA</t>
   </si>
   <si>
@@ -219,6 +225,9 @@
   </si>
   <si>
     <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
   </si>
   <si>
     <t>ADRIAN</t>
@@ -1147,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1262,7 +1271,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -1316,7 +1325,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1407,7 +1416,7 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -1425,7 +1434,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -4496,7 +4505,7 @@
         <v>11.5</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4516,16 +4525,16 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="G4" s="2">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -4674,7 +4683,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4706,22 +4715,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920002</v>
+        <v>22330051920213</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4729,16 +4738,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920374</v>
+        <v>22330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
         <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4752,24 +4761,70 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920222</v>
+        <v>21330051920002</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
         <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920222</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
         <v>52</v>
       </c>
-      <c r="G4">
+      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20231.xlsx
+++ b/grupos/3ARHV - Estadisticos 20231.xlsx
@@ -780,19 +780,19 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -857,22 +857,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -940,13 +940,13 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1020,10 +1020,10 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1088,22 +1088,22 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1242,22 +1242,22 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1328,10 +1328,10 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1360,10 +1360,10 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1425,19 +1425,19 @@
         <v>7</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1502,19 +1502,19 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1585,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1659,19 +1659,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1733,22 +1733,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1810,10 +1810,10 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1884,13 +1884,13 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1958,13 +1958,13 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2032,19 +2032,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2112,13 +2112,13 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2183,22 +2183,22 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2266,13 +2266,13 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2340,19 +2340,19 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2414,22 +2414,22 @@
         <v>8</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2500,13 +2500,13 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2725,19 +2725,19 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4473,7 +4473,7 @@
         <v>16</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4505,7 +4505,7 @@
         <v>11.5</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         <v>3.8</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>3.8</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4601,7 +4601,7 @@
         <v>3.7</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         <v>3.7</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ARHV - Estadisticos 20231.xlsx
+++ b/grupos/3ARHV - Estadisticos 20231.xlsx
@@ -780,19 +780,19 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -857,22 +857,22 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -940,13 +940,13 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1020,10 +1020,10 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1088,22 +1088,22 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1242,22 +1242,22 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1328,10 +1328,10 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1360,10 +1360,10 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1425,19 +1425,19 @@
         <v>7</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1502,19 +1502,19 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1585,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1659,19 +1659,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1733,22 +1733,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1810,10 +1810,10 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1884,13 +1884,13 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1958,13 +1958,13 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2032,19 +2032,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2112,13 +2112,13 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2183,22 +2183,22 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2266,13 +2266,13 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2340,19 +2340,19 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2414,22 +2414,22 @@
         <v>8</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2500,13 +2500,13 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2725,19 +2725,19 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4473,7 +4473,7 @@
         <v>16</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4505,7 +4505,7 @@
         <v>11.5</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         <v>3.8</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>3.8</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4601,7 +4601,7 @@
         <v>3.7</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         <v>3.7</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
